--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-03-08.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-03-08.xlsx
@@ -757,10 +757,10 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G2" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
         <v>3.85</v>
@@ -775,40 +775,40 @@
         <v>3.85</v>
       </c>
       <c r="L2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="M2" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N2" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="O2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P2" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="T2" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="V2" t="n">
         <v>1.32</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
         <v>17</v>
@@ -823,19 +823,19 @@
         <v>85</v>
       </c>
       <c r="AB2" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC2" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
         <v>17.5</v>
       </c>
       <c r="AE2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AF2" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -859,34 +859,34 @@
         <v>100</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>15.5</v>
       </c>
       <c r="AO2" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="AP2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AR2" t="n">
         <v>26</v>
       </c>
       <c r="AS2" t="n">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT2" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="AU2" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV2" t="n">
         <v>14</v>
       </c>
       <c r="AW2" t="n">
-        <v>7.6</v>
+        <v>32</v>
       </c>
       <c r="AX2" t="n">
         <v>11</v>
@@ -895,10 +895,10 @@
         <v>9.4</v>
       </c>
       <c r="AZ2" t="n">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA2" t="n">
-        <v>38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB2" t="n">
         <v>20</v>
@@ -907,20 +907,20 @@
         <v>17.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE2" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BG2" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="BF2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>7.6</v>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -975,16 +975,16 @@
         <v>1.01</v>
       </c>
       <c r="N3" t="n">
-        <v>2.36</v>
+        <v>1.04</v>
       </c>
       <c r="O3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P3" t="n">
-        <v>2.36</v>
+        <v>1.48</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="R3" t="n">
         <v>1.48</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="G4" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="H4" t="n">
         <v>10.5</v>
@@ -1157,10 +1157,10 @@
         <v>16</v>
       </c>
       <c r="J4" t="n">
-        <v>4.6</v>
+        <v>4.9</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="L4" t="n">
         <v>1.33</v>
@@ -1196,7 +1196,7 @@
         <v>1.07</v>
       </c>
       <c r="W4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="X4" t="n">
         <v>18.5</v>
@@ -1211,7 +1211,7 @@
         <v>1000</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AC4" t="n">
         <v>14</v>
@@ -1241,7 +1241,7 @@
         <v>19.5</v>
       </c>
       <c r="AL4" t="n">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AM4" t="n">
         <v>1000</v>
@@ -1253,62 +1253,62 @@
         <v>1000</v>
       </c>
       <c r="AP4" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AQ4" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="AR4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AS4" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT4" t="n">
         <v>6.2</v>
       </c>
       <c r="AU4" t="n">
-        <v>4.5</v>
+        <v>10.5</v>
       </c>
       <c r="AV4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AW4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="AX4" t="n">
         <v>6.2</v>
       </c>
       <c r="AY4" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="AZ4" t="n">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BA4" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BB4" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BD4" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BE4" t="n">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF4" t="n">
         <v>5.4</v>
       </c>
       <c r="BG4" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1560,19 +1560,19 @@
         <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P6" t="n">
         <v>1.24</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="R6" t="n">
         <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="T6" t="n">
         <v>1.01</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1736,7 @@
         <v>2.88</v>
       </c>
       <c r="I7" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="J7" t="n">
         <v>3.45</v>
@@ -1760,13 +1760,13 @@
         <v>2.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
         <v>1.39</v>
       </c>
       <c r="S7" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T7" t="n">
         <v>1.01</v>
@@ -1775,7 +1775,7 @@
         <v>1.01</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W7" t="n">
         <v>1.72</v>
@@ -1835,16 +1835,16 @@
         <v>1000</v>
       </c>
       <c r="AP7" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AR7" t="n">
         <v>20</v>
       </c>
       <c r="AS7" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AT7" t="n">
         <v>9.4</v>
@@ -1859,7 +1859,7 @@
         <v>26</v>
       </c>
       <c r="AX7" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AY7" t="n">
         <v>9</v>
@@ -1868,19 +1868,19 @@
         <v>11.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="BB7" t="n">
         <v>20</v>
       </c>
       <c r="BC7" t="n">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="BD7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BE7" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BF7" t="n">
         <v>1.01</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2127,7 @@
         <v>6.8</v>
       </c>
       <c r="J9" t="n">
-        <v>2.44</v>
+        <v>2.92</v>
       </c>
       <c r="K9" t="n">
         <v>1000</v>
@@ -2160,10 +2160,10 @@
         <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
         <v>1.8</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -2315,16 +2315,16 @@
         <v>4.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I10" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="J10" t="n">
         <v>4.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L10" t="n">
         <v>1.23</v>
@@ -2354,13 +2354,13 @@
         <v>1.54</v>
       </c>
       <c r="U10" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="V10" t="n">
         <v>2.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X10" t="n">
         <v>70</v>
@@ -2462,17 +2462,17 @@
         <v>29</v>
       </c>
       <c r="BE10" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BF10" t="n">
         <v>21</v>
       </c>
       <c r="BG10" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -2503,46 +2503,46 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="G11" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I11" t="n">
         <v>3.85</v>
       </c>
       <c r="J11" t="n">
-        <v>2.86</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
         <v>1.08</v>
       </c>
       <c r="N11" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O11" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P11" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R11" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S11" t="n">
-        <v>3.35</v>
+        <v>3.85</v>
       </c>
       <c r="T11" t="n">
         <v>1.7</v>
@@ -2551,16 +2551,16 @@
         <v>1.86</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
         <v>1.62</v>
       </c>
       <c r="X11" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Z11" t="n">
         <v>29</v>
@@ -2575,7 +2575,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD11" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE11" t="n">
         <v>55</v>
@@ -2596,7 +2596,7 @@
         <v>42</v>
       </c>
       <c r="AK11" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AL11" t="n">
         <v>55</v>
@@ -2605,68 +2605,68 @@
         <v>140</v>
       </c>
       <c r="AN11" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="AO11" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AP11" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AR11" t="n">
-        <v>17</v>
+        <v>3.7</v>
       </c>
       <c r="AS11" t="n">
         <v>4</v>
       </c>
       <c r="AT11" t="n">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="AU11" t="n">
-        <v>2.92</v>
+        <v>5.7</v>
       </c>
       <c r="AV11" t="n">
         <v>10.5</v>
       </c>
       <c r="AW11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AX11" t="n">
         <v>11</v>
       </c>
       <c r="AY11" t="n">
-        <v>3.25</v>
+        <v>8.6</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3.6</v>
+        <v>13.5</v>
       </c>
       <c r="BA11" t="n">
         <v>4</v>
       </c>
       <c r="BB11" t="n">
-        <v>3.9</v>
+        <v>24</v>
       </c>
       <c r="BC11" t="n">
         <v>20</v>
       </c>
       <c r="BD11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="BE11" t="n">
         <v>4.1</v>
       </c>
       <c r="BF11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BG11" t="n">
         <v>3.95</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -2700,10 +2700,10 @@
         <v>2.28</v>
       </c>
       <c r="G12" t="n">
-        <v>3.15</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>2.84</v>
       </c>
       <c r="I12" t="n">
         <v>4</v>
@@ -2712,7 +2712,7 @@
         <v>2.74</v>
       </c>
       <c r="K12" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L12" t="n">
         <v>1.35</v>
@@ -2733,10 +2733,10 @@
         <v>1.96</v>
       </c>
       <c r="R12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S12" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T12" t="n">
         <v>1.68</v>
@@ -2748,7 +2748,7 @@
         <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2805,49 +2805,49 @@
         <v>1000</v>
       </c>
       <c r="AP12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AQ12" t="n">
         <v>9</v>
       </c>
       <c r="AR12" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AS12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AT12" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AU12" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX12" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AY12" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AZ12" t="n">
         <v>15.5</v>
       </c>
       <c r="BA12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BB12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="BC12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE12" t="n">
         <v>50</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
         <v>4.6</v>
       </c>
       <c r="L14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="M14" t="n">
         <v>1.04</v>
@@ -3115,7 +3115,7 @@
         <v>1.19</v>
       </c>
       <c r="P14" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="Q14" t="n">
         <v>1.57</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3557,7 +3557,7 @@
         <v>12.5</v>
       </c>
       <c r="AH16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AI16" t="n">
         <v>100</v>
@@ -3626,7 +3626,7 @@
         <v>34</v>
       </c>
       <c r="BE16" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BF16" t="n">
         <v>29</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G17" t="n">
         <v>2.64</v>
@@ -3676,13 +3676,13 @@
         <v>3.15</v>
       </c>
       <c r="I17" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="J17" t="n">
         <v>2.78</v>
       </c>
       <c r="K17" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="L17" t="n">
         <v>1.39</v>
@@ -3715,7 +3715,7 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W17" t="n">
         <v>1.6</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -3870,10 +3870,10 @@
         <v>4.4</v>
       </c>
       <c r="I18" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="J18" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K18" t="n">
         <v>3.8</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
         <v>3.75</v>
       </c>
       <c r="I20" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="J20" t="n">
         <v>3.75</v>
@@ -4291,13 +4291,13 @@
         <v>2.2</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="U20" t="n">
         <v>2.32</v>
       </c>
       <c r="V20" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W20" t="n">
         <v>2</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4443,22 +4443,22 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="G21" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="H21" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="I21" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J21" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K21" t="n">
         <v>3.75</v>
-      </c>
-      <c r="K21" t="n">
-        <v>3.8</v>
       </c>
       <c r="L21" t="n">
         <v>1.34</v>
@@ -4467,7 +4467,7 @@
         <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.26</v>
@@ -4479,10 +4479,10 @@
         <v>1.77</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="S21" t="n">
-        <v>2.52</v>
+        <v>2.88</v>
       </c>
       <c r="T21" t="n">
         <v>1.64</v>
@@ -4491,10 +4491,10 @@
         <v>2.4</v>
       </c>
       <c r="V21" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="W21" t="n">
         <v>1.54</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.57</v>
       </c>
       <c r="X21" t="n">
         <v>22</v>
@@ -4533,10 +4533,10 @@
         <v>36</v>
       </c>
       <c r="AJ21" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AK21" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AL21" t="n">
         <v>36</v>
@@ -4548,7 +4548,7 @@
         <v>23</v>
       </c>
       <c r="AO21" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AP21" t="n">
         <v>16</v>
@@ -4557,7 +4557,7 @@
         <v>12</v>
       </c>
       <c r="AR21" t="n">
-        <v>6.6</v>
+        <v>17</v>
       </c>
       <c r="AS21" t="n">
         <v>7.8</v>
@@ -4584,16 +4584,16 @@
         <v>13.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BB21" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BC21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD21" t="n">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BE21" t="n">
         <v>8.4</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
         <v>1.44</v>
       </c>
       <c r="H22" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="I22" t="n">
         <v>8.4</v>
@@ -4676,10 +4676,10 @@
         <v>1.67</v>
       </c>
       <c r="S22" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="T22" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="U22" t="n">
         <v>2.12</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -4837,7 +4837,7 @@
         <v>3.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I23" t="n">
         <v>2.34</v>
@@ -4876,7 +4876,7 @@
         <v>1.67</v>
       </c>
       <c r="U23" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="V23" t="n">
         <v>1.74</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="H24" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="I24" t="n">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="J24" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K24" t="n">
-        <v>4.9</v>
+        <v>7</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5049,19 +5049,19 @@
         <v>1.01</v>
       </c>
       <c r="N24" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="O24" t="n">
         <v>1.17</v>
       </c>
       <c r="P24" t="n">
-        <v>2.36</v>
+        <v>2.04</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S24" t="n">
         <v>2.2</v>
@@ -5073,10 +5073,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>1.68</v>
+        <v>1.63</v>
       </c>
       <c r="X24" t="n">
         <v>32</v>
@@ -5151,7 +5151,7 @@
         <v>1.94</v>
       </c>
       <c r="AV24" t="n">
-        <v>10</v>
+        <v>2.04</v>
       </c>
       <c r="AW24" t="n">
         <v>2.16</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         <v>1.06</v>
       </c>
       <c r="N25" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
         <v>1.39</v>
@@ -5336,13 +5336,13 @@
         <v>23</v>
       </c>
       <c r="AS25" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AT25" t="n">
         <v>6.6</v>
       </c>
       <c r="AU25" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV25" t="n">
         <v>15</v>
@@ -5360,19 +5360,19 @@
         <v>18</v>
       </c>
       <c r="BA25" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BB25" t="n">
         <v>18.5</v>
       </c>
       <c r="BC25" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD25" t="n">
         <v>34</v>
       </c>
       <c r="BE25" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="BF25" t="n">
         <v>1.01</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G26" t="n">
         <v>2.68</v>
@@ -5422,16 +5422,16 @@
         <v>3.1</v>
       </c>
       <c r="I26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="J26" t="n">
         <v>2.76</v>
       </c>
       <c r="K26" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="M26" t="n">
         <v>1.01</v>
@@ -5461,7 +5461,7 @@
         <v>1.01</v>
       </c>
       <c r="V26" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W26" t="n">
         <v>1.59</v>
@@ -5521,49 +5521,49 @@
         <v>1000</v>
       </c>
       <c r="AP26" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
         <v>9</v>
       </c>
       <c r="AR26" t="n">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AS26" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AT26" t="n">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AU26" t="n">
         <v>6.2</v>
       </c>
       <c r="AV26" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AW26" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AX26" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY26" t="n">
         <v>9.4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BA26" t="n">
         <v>46</v>
       </c>
       <c r="BB26" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="BC26" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BD26" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BE26" t="n">
         <v>50</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L27" t="n">
         <v>1.31</v>
@@ -5631,34 +5631,34 @@
         <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>23</v>
@@ -5700,7 +5700,7 @@
         <v>14.5</v>
       </c>
       <c r="AK27" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AL27" t="n">
         <v>29</v>
@@ -5721,7 +5721,7 @@
         <v>25</v>
       </c>
       <c r="AR27" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AS27" t="n">
         <v>46</v>
@@ -5748,7 +5748,7 @@
         <v>18.5</v>
       </c>
       <c r="BA27" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="BB27" t="n">
         <v>13</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
         <v>2.96</v>
       </c>
       <c r="T28" t="n">
-        <v>1.01</v>
+        <v>1.72</v>
       </c>
       <c r="U28" t="n">
         <v>1.01</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -5995,10 +5995,10 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="G29" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="H29" t="n">
         <v>4.4</v>
@@ -6010,7 +6010,7 @@
         <v>3.85</v>
       </c>
       <c r="K29" t="n">
-        <v>7.6</v>
+        <v>110</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -6213,22 +6213,22 @@
         <v>1.04</v>
       </c>
       <c r="N30" t="n">
-        <v>2.26</v>
+        <v>1.04</v>
       </c>
       <c r="O30" t="n">
         <v>1.22</v>
       </c>
       <c r="P30" t="n">
-        <v>2.26</v>
+        <v>1.46</v>
       </c>
       <c r="Q30" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="R30" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S30" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="T30" t="n">
         <v>1.55</v>
@@ -6237,7 +6237,7 @@
         <v>2.2</v>
       </c>
       <c r="V30" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W30" t="n">
         <v>1.8</v>
@@ -6246,49 +6246,49 @@
         <v>1000</v>
       </c>
       <c r="Y30" t="n">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Z30" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AA30" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AB30" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC30" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD30" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE30" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AF30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG30" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH30" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI30" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK30" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL30" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM30" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN30" t="n">
         <v>1000</v>
@@ -6297,62 +6297,62 @@
         <v>1000</v>
       </c>
       <c r="AP30" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AQ30" t="n">
-        <v>1.01</v>
+        <v>1.97</v>
       </c>
       <c r="AR30" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="AS30" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="AT30" t="n">
-        <v>1.01</v>
+        <v>1.92</v>
       </c>
       <c r="AU30" t="n">
-        <v>1.01</v>
+        <v>1.84</v>
       </c>
       <c r="AV30" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="AW30" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="AX30" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="AY30" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="AZ30" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BA30" t="n">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BB30" t="n">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BC30" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="BD30" t="n">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BE30" t="n">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="BF30" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BG30" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -6383,7 +6383,7 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G31" t="n">
         <v>4.7</v>
@@ -6392,7 +6392,7 @@
         <v>1.79</v>
       </c>
       <c r="I31" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="J31" t="n">
         <v>4.1</v>
@@ -6407,7 +6407,7 @@
         <v>1.04</v>
       </c>
       <c r="N31" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
         <v>1.2</v>
@@ -6416,16 +6416,16 @@
         <v>2.46</v>
       </c>
       <c r="Q31" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="S31" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="T31" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="U31" t="n">
         <v>2.4</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -6601,7 +6601,7 @@
         <v>1.01</v>
       </c>
       <c r="N32" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="O32" t="n">
         <v>1.33</v>
@@ -6610,7 +6610,7 @@
         <v>1.18</v>
       </c>
       <c r="Q32" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="R32" t="n">
         <v>1.18</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -6771,10 +6771,10 @@
         </is>
       </c>
       <c r="F33" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="G33" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="H33" t="n">
         <v>2.48</v>
@@ -6795,13 +6795,13 @@
         <v>1.01</v>
       </c>
       <c r="N33" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O33" t="n">
         <v>1.35</v>
       </c>
       <c r="P33" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q33" t="n">
         <v>1.94</v>
@@ -6822,7 +6822,7 @@
         <v>1.4</v>
       </c>
       <c r="W33" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X33" t="n">
         <v>1000</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="G35" t="n">
         <v>3</v>
@@ -7177,7 +7177,7 @@
         <v>5</v>
       </c>
       <c r="L35" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="M35" t="n">
         <v>1.01</v>
@@ -7192,13 +7192,13 @@
         <v>1.39</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="R35" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="S35" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="T35" t="n">
         <v>1.01</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
         <v>1.88</v>
       </c>
       <c r="O36" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="P36" t="n">
         <v>1.88</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7571,7 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="O37" t="n">
         <v>1.25</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -7849,7 +7849,7 @@
         <v>1000</v>
       </c>
       <c r="AP38" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AQ38" t="n">
         <v>9.199999999999999</v>
@@ -7861,7 +7861,7 @@
         <v>25</v>
       </c>
       <c r="AT38" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AU38" t="n">
         <v>6.8</v>
@@ -7870,28 +7870,28 @@
         <v>9.4</v>
       </c>
       <c r="AW38" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AX38" t="n">
         <v>16</v>
       </c>
       <c r="AY38" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ38" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA38" t="n">
         <v>26</v>
       </c>
       <c r="BB38" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BC38" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD38" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BE38" t="n">
         <v>48</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -7977,10 +7977,10 @@
         <v>3.25</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
         <v>1.4</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="G40" t="n">
         <v>2.92</v>
@@ -8144,7 +8144,7 @@
         <v>3.25</v>
       </c>
       <c r="K40" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L40" t="n">
         <v>1.01</v>
@@ -8156,13 +8156,13 @@
         <v>3.1</v>
       </c>
       <c r="O40" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P40" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="R40" t="n">
         <v>1.27</v>
@@ -8174,10 +8174,10 @@
         <v>1.87</v>
       </c>
       <c r="U40" t="n">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="V40" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W40" t="n">
         <v>1.52</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -8344,25 +8344,25 @@
         <v>1.01</v>
       </c>
       <c r="M41" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N41" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="O41" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P41" t="n">
-        <v>1.98</v>
+        <v>1.83</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R41" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S41" t="n">
-        <v>3.25</v>
+        <v>2.88</v>
       </c>
       <c r="T41" t="n">
         <v>1.81</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
         <v>2.34</v>
       </c>
       <c r="G42" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H42" t="n">
         <v>3.25</v>
@@ -8568,7 +8568,7 @@
         <v>1.38</v>
       </c>
       <c r="W42" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X42" t="n">
         <v>16</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -8720,13 +8720,13 @@
         <v>6.8</v>
       </c>
       <c r="I43" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="J43" t="n">
         <v>3.95</v>
       </c>
       <c r="K43" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L43" t="n">
         <v>1.45</v>
@@ -8750,7 +8750,7 @@
         <v>1.31</v>
       </c>
       <c r="S43" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T43" t="n">
         <v>2.18</v>
@@ -8789,7 +8789,7 @@
         <v>120</v>
       </c>
       <c r="AF43" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG43" t="n">
         <v>10.5</v>
@@ -8828,7 +8828,7 @@
         <v>48</v>
       </c>
       <c r="AS43" t="n">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="AT43" t="n">
         <v>6.8</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -8932,7 +8932,7 @@
         <v>1.03</v>
       </c>
       <c r="O44" t="n">
-        <v>1.41</v>
+        <v>1.09</v>
       </c>
       <c r="P44" t="n">
         <v>1.2</v>
@@ -8947,7 +8947,7 @@
         <v>3.6</v>
       </c>
       <c r="T44" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U44" t="n">
         <v>1.01</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -9135,10 +9135,10 @@
         <v>1.55</v>
       </c>
       <c r="R45" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="S45" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="T45" t="n">
         <v>2.04</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -9520,7 +9520,7 @@
         <v>1.73</v>
       </c>
       <c r="Q47" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="R47" t="n">
         <v>1.25</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -9792,31 +9792,31 @@
         <v>7</v>
       </c>
       <c r="AQ48" t="n">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AR48" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AS48" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AT48" t="n">
         <v>5.7</v>
       </c>
       <c r="AU48" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV48" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW48" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AX48" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AY48" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AY48" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AZ48" t="n">
         <v>21</v>
@@ -9825,13 +9825,13 @@
         <v>50</v>
       </c>
       <c r="BB48" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BC48" t="n">
         <v>24</v>
       </c>
       <c r="BD48" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE48" t="n">
         <v>50</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -10069,7 +10069,7 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G50" t="n">
         <v>4.4</v>
@@ -10093,16 +10093,16 @@
         <v>1.01</v>
       </c>
       <c r="N50" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="O50" t="n">
         <v>1.31</v>
       </c>
       <c r="P50" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R50" t="n">
         <v>1.28</v>
@@ -10117,7 +10117,7 @@
         <v>1.01</v>
       </c>
       <c r="V50" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="W50" t="n">
         <v>1.29</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -10266,16 +10266,16 @@
         <v>2.14</v>
       </c>
       <c r="G51" t="n">
-        <v>110</v>
+        <v>2.54</v>
       </c>
       <c r="H51" t="n">
-        <v>1.09</v>
+        <v>2.9</v>
       </c>
       <c r="I51" t="n">
         <v>3.65</v>
       </c>
       <c r="J51" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="K51" t="n">
         <v>950</v>
@@ -10426,7 +10426,7 @@
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -10481,7 +10481,7 @@
         <v>1.08</v>
       </c>
       <c r="N52" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O52" t="n">
         <v>1.35</v>
@@ -10493,7 +10493,7 @@
         <v>2.04</v>
       </c>
       <c r="R52" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S52" t="n">
         <v>3.65</v>
@@ -10511,7 +10511,7 @@
         <v>1.48</v>
       </c>
       <c r="X52" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y52" t="n">
         <v>11</v>
@@ -10550,7 +10550,7 @@
         <v>55</v>
       </c>
       <c r="AK52" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL52" t="n">
         <v>48</v>
@@ -10601,7 +10601,7 @@
         <v>38</v>
       </c>
       <c r="BB52" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BC52" t="n">
         <v>27</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -11039,22 +11039,22 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G55" t="n">
         <v>3.4</v>
       </c>
       <c r="H55" t="n">
-        <v>2.38</v>
+        <v>2.08</v>
       </c>
       <c r="I55" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J55" t="n">
         <v>2.8</v>
       </c>
       <c r="K55" t="n">
-        <v>7.2</v>
+        <v>110</v>
       </c>
       <c r="L55" t="n">
         <v>1.34</v>
@@ -11087,7 +11087,7 @@
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W55" t="n">
         <v>1.41</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -11233,7 +11233,7 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G56" t="n">
         <v>2.58</v>
@@ -11371,7 +11371,7 @@
         <v>10</v>
       </c>
       <c r="AZ56" t="n">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BA56" t="n">
         <v>7.8</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -11451,7 +11451,7 @@
         <v>1.01</v>
       </c>
       <c r="N57" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="O57" t="n">
         <v>1.01</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -11657,7 +11657,7 @@
         <v>2.06</v>
       </c>
       <c r="R58" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S58" t="n">
         <v>3.75</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -12209,13 +12209,13 @@
         <v>5.5</v>
       </c>
       <c r="H61" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="I61" t="n">
         <v>1.93</v>
       </c>
       <c r="J61" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K61" t="n">
         <v>3.6</v>
@@ -12227,28 +12227,28 @@
         <v>1.09</v>
       </c>
       <c r="N61" t="n">
-        <v>2.98</v>
+        <v>3.1</v>
       </c>
       <c r="O61" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P61" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R61" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="S61" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="T61" t="n">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="U61" t="n">
-        <v>1.83</v>
+        <v>1.87</v>
       </c>
       <c r="V61" t="n">
         <v>2.06</v>
@@ -12257,10 +12257,10 @@
         <v>1.24</v>
       </c>
       <c r="X61" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Y61" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="Z61" t="n">
         <v>11</v>
@@ -12269,7 +12269,7 @@
         <v>23</v>
       </c>
       <c r="AB61" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC61" t="n">
         <v>8</v>
@@ -12296,22 +12296,22 @@
         <v>170</v>
       </c>
       <c r="AK61" t="n">
+        <v>100</v>
+      </c>
+      <c r="AL61" t="n">
         <v>110</v>
       </c>
-      <c r="AL61" t="n">
-        <v>120</v>
-      </c>
       <c r="AM61" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN61" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AO61" t="n">
         <v>21</v>
       </c>
       <c r="AP61" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ61" t="n">
         <v>6.4</v>
@@ -12320,7 +12320,7 @@
         <v>9.4</v>
       </c>
       <c r="AS61" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AT61" t="n">
         <v>12.5</v>
@@ -12335,38 +12335,38 @@
         <v>20</v>
       </c>
       <c r="AX61" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY61" t="n">
         <v>16.5</v>
       </c>
       <c r="AZ61" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="BA61" t="n">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="BB61" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC61" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BD61" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BE61" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF61" t="n">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG61" t="n">
         <v>13.5</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -12397,7 +12397,7 @@
         </is>
       </c>
       <c r="F62" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G62" t="n">
         <v>1.68</v>
@@ -12439,10 +12439,10 @@
         <v>2.7</v>
       </c>
       <c r="T62" t="n">
-        <v>1.8</v>
+        <v>1.71</v>
       </c>
       <c r="U62" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="V62" t="n">
         <v>1.14</v>
@@ -12523,13 +12523,13 @@
         <v>3.75</v>
       </c>
       <c r="AV62" t="n">
-        <v>4.6</v>
+        <v>18</v>
       </c>
       <c r="AW62" t="n">
         <v>5.3</v>
       </c>
       <c r="AX62" t="n">
-        <v>7.4</v>
+        <v>3.8</v>
       </c>
       <c r="AY62" t="n">
         <v>3.8</v>
@@ -12560,7 +12560,7 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -12603,7 +12603,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K63" t="n">
         <v>4.9</v>
@@ -12714,7 +12714,7 @@
         <v>6</v>
       </c>
       <c r="AU63" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV63" t="n">
         <v>4.7</v>
@@ -12729,7 +12729,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ63" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA63" t="n">
         <v>5.2</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -12791,7 +12791,7 @@
         <v>1.71</v>
       </c>
       <c r="H64" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="I64" t="n">
         <v>1000</v>
@@ -12806,34 +12806,34 @@
         <v>1.01</v>
       </c>
       <c r="M64" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N64" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="O64" t="n">
         <v>1.11</v>
       </c>
       <c r="P64" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="R64" t="n">
         <v>1.71</v>
       </c>
       <c r="S64" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="T64" t="n">
-        <v>1.01</v>
+        <v>1.49</v>
       </c>
       <c r="U64" t="n">
         <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="W64" t="n">
         <v>2.42</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G65" t="n">
         <v>4.5</v>
@@ -12994,7 +12994,7 @@
         <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L65" t="n">
         <v>1.31</v>
@@ -13009,10 +13009,10 @@
         <v>1.24</v>
       </c>
       <c r="P65" t="n">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="R65" t="n">
         <v>1.49</v>
@@ -13117,7 +13117,7 @@
         <v>13</v>
       </c>
       <c r="AZ65" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA65" t="n">
         <v>5.2</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -13185,7 +13185,7 @@
         <v>4.4</v>
       </c>
       <c r="J66" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K66" t="n">
         <v>4.1</v>
@@ -13281,7 +13281,7 @@
         <v>46</v>
       </c>
       <c r="AP66" t="n">
-        <v>4.5</v>
+        <v>15.5</v>
       </c>
       <c r="AQ66" t="n">
         <v>15</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -13370,19 +13370,19 @@
         <v>1.84</v>
       </c>
       <c r="G67" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="H67" t="n">
         <v>4.4</v>
       </c>
       <c r="I67" t="n">
-        <v>1000</v>
+        <v>7</v>
       </c>
       <c r="J67" t="n">
-        <v>1.09</v>
+        <v>2.78</v>
       </c>
       <c r="K67" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="L67" t="n">
         <v>1.01</v>
@@ -13415,10 +13415,10 @@
         <v>1.01</v>
       </c>
       <c r="V67" t="n">
-        <v>1.21</v>
+        <v>1.16</v>
       </c>
       <c r="W67" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="X67" t="n">
         <v>1000</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -13561,22 +13561,22 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="G68" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="H68" t="n">
         <v>4.1</v>
       </c>
       <c r="I68" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J68" t="n">
         <v>3.15</v>
       </c>
       <c r="K68" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L68" t="n">
         <v>1.01</v>
@@ -13585,16 +13585,16 @@
         <v>1.1</v>
       </c>
       <c r="N68" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="O68" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P68" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R68" t="n">
         <v>1.24</v>
@@ -13612,7 +13612,7 @@
         <v>1.27</v>
       </c>
       <c r="W68" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="X68" t="n">
         <v>1000</v>
@@ -13675,7 +13675,7 @@
         <v>2.02</v>
       </c>
       <c r="AR68" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AS68" t="n">
         <v>2.28</v>
@@ -13705,7 +13705,7 @@
         <v>2.24</v>
       </c>
       <c r="BB68" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC68" t="n">
         <v>2.16</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -13755,16 +13755,16 @@
         </is>
       </c>
       <c r="F69" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G69" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="H69" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="I69" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J69" t="n">
         <v>3.05</v>
@@ -13779,10 +13779,10 @@
         <v>1.1</v>
       </c>
       <c r="N69" t="n">
-        <v>2.92</v>
+        <v>1.57</v>
       </c>
       <c r="O69" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="P69" t="n">
         <v>1.56</v>
@@ -13797,16 +13797,16 @@
         <v>3.75</v>
       </c>
       <c r="T69" t="n">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U69" t="n">
-        <v>1.68</v>
+        <v>1.01</v>
       </c>
       <c r="V69" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="W69" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="X69" t="n">
         <v>1000</v>
@@ -13818,7 +13818,7 @@
         <v>29</v>
       </c>
       <c r="AA69" t="n">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="AB69" t="n">
         <v>12.5</v>
@@ -13827,10 +13827,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD69" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AE69" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF69" t="n">
         <v>23</v>
@@ -13863,62 +13863,62 @@
         <v>1000</v>
       </c>
       <c r="AP69" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AQ69" t="n">
-        <v>8.6</v>
+        <v>2.02</v>
       </c>
       <c r="AR69" t="n">
         <v>15</v>
       </c>
       <c r="AS69" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AW69" t="n">
         <v>2.24</v>
       </c>
-      <c r="AT69" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AU69" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AV69" t="n">
+      <c r="AX69" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AY69" t="n">
         <v>2.06</v>
       </c>
-      <c r="AW69" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="AX69" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AY69" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AZ69" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BA69" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="BB69" t="n">
         <v>2.24</v>
       </c>
-      <c r="BB69" t="n">
-        <v>2.22</v>
-      </c>
       <c r="BC69" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="BD69" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="BE69" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BF69" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BG69" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -13952,13 +13952,13 @@
         <v>1.04</v>
       </c>
       <c r="G70" t="n">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="H70" t="n">
         <v>2.12</v>
       </c>
       <c r="I70" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J70" t="n">
         <v>1.03</v>
@@ -13997,7 +13997,7 @@
         <v>1.01</v>
       </c>
       <c r="V70" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W70" t="n">
         <v>1.64</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -14143,22 +14143,22 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="G71" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H71" t="n">
         <v>2.36</v>
       </c>
       <c r="I71" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J71" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K71" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L71" t="n">
         <v>1.01</v>
@@ -14191,10 +14191,10 @@
         <v>2.28</v>
       </c>
       <c r="V71" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W71" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="X71" t="n">
         <v>17</v>
@@ -14206,10 +14206,10 @@
         <v>16.5</v>
       </c>
       <c r="AA71" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AB71" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AC71" t="n">
         <v>8.199999999999999</v>
@@ -14245,13 +14245,13 @@
         <v>80</v>
       </c>
       <c r="AN71" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AO71" t="n">
         <v>17</v>
       </c>
       <c r="AP71" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AQ71" t="n">
         <v>10.5</v>
@@ -14266,7 +14266,7 @@
         <v>13</v>
       </c>
       <c r="AU71" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AV71" t="n">
         <v>10</v>
@@ -14275,7 +14275,7 @@
         <v>20</v>
       </c>
       <c r="AX71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY71" t="n">
         <v>12.5</v>
@@ -14299,14 +14299,14 @@
         <v>10.5</v>
       </c>
       <c r="BF71" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG71" t="n">
         <v>13.5</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -14337,22 +14337,22 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="G72" t="n">
         <v>2.58</v>
       </c>
       <c r="H72" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I72" t="n">
         <v>1000</v>
       </c>
       <c r="J72" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="K72" t="n">
-        <v>4.4</v>
+        <v>950</v>
       </c>
       <c r="L72" t="n">
         <v>1.01</v>
@@ -14370,16 +14370,16 @@
         <v>1.58</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="R72" t="n">
         <v>1.21</v>
       </c>
       <c r="S72" t="n">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="T72" t="n">
-        <v>1.76</v>
+        <v>1.82</v>
       </c>
       <c r="U72" t="n">
         <v>1.01</v>
@@ -14388,10 +14388,10 @@
         <v>1.01</v>
       </c>
       <c r="W72" t="n">
-        <v>1.63</v>
+        <v>1.42</v>
       </c>
       <c r="X72" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="Y72" t="n">
         <v>15.5</v>
@@ -14403,7 +14403,7 @@
         <v>90</v>
       </c>
       <c r="AB72" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AC72" t="n">
         <v>10</v>
@@ -14445,62 +14445,62 @@
         <v>1000</v>
       </c>
       <c r="AP72" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AQ72" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="AR72" t="n">
         <v>16.5</v>
       </c>
       <c r="AS72" t="n">
-        <v>2.28</v>
+        <v>2.82</v>
       </c>
       <c r="AT72" t="n">
-        <v>1.96</v>
+        <v>2.32</v>
       </c>
       <c r="AU72" t="n">
         <v>6.2</v>
       </c>
       <c r="AV72" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="AW72" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="AX72" t="n">
-        <v>2.1</v>
+        <v>2.54</v>
       </c>
       <c r="AY72" t="n">
-        <v>2.04</v>
+        <v>2.46</v>
       </c>
       <c r="AZ72" t="n">
-        <v>2.16</v>
+        <v>2.64</v>
       </c>
       <c r="BA72" t="n">
-        <v>2.28</v>
+        <v>2.82</v>
       </c>
       <c r="BB72" t="n">
-        <v>2.24</v>
+        <v>2.74</v>
       </c>
       <c r="BC72" t="n">
-        <v>2.22</v>
+        <v>2.74</v>
       </c>
       <c r="BD72" t="n">
-        <v>2.26</v>
+        <v>2.78</v>
       </c>
       <c r="BE72" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="BF72" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="BG72" t="n">
-        <v>2.34</v>
+        <v>2.92</v>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -14534,7 +14534,7 @@
         <v>1.6</v>
       </c>
       <c r="G73" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="H73" t="n">
         <v>6.4</v>
@@ -14555,16 +14555,16 @@
         <v>1.06</v>
       </c>
       <c r="N73" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="O73" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P73" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q73" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="R73" t="n">
         <v>1.38</v>
@@ -14582,13 +14582,13 @@
         <v>1.17</v>
       </c>
       <c r="W73" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X73" t="n">
         <v>15</v>
       </c>
       <c r="Y73" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z73" t="n">
         <v>55</v>
@@ -14609,7 +14609,7 @@
         <v>110</v>
       </c>
       <c r="AF73" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AG73" t="n">
         <v>10</v>
@@ -14624,10 +14624,10 @@
         <v>15</v>
       </c>
       <c r="AK73" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AL73" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AM73" t="n">
         <v>150</v>
@@ -14636,7 +14636,7 @@
         <v>9.4</v>
       </c>
       <c r="AO73" t="n">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP73" t="n">
         <v>14</v>
@@ -14648,10 +14648,10 @@
         <v>46</v>
       </c>
       <c r="AS73" t="n">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="AT73" t="n">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AU73" t="n">
         <v>8.6</v>
@@ -14660,19 +14660,19 @@
         <v>22</v>
       </c>
       <c r="AW73" t="n">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="AX73" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="AY73" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ73" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA73" t="n">
-        <v>15.5</v>
+        <v>38</v>
       </c>
       <c r="BB73" t="n">
         <v>13.5</v>
@@ -14684,17 +14684,17 @@
         <v>32</v>
       </c>
       <c r="BE73" t="n">
-        <v>16</v>
+        <v>44</v>
       </c>
       <c r="BF73" t="n">
         <v>8.4</v>
       </c>
       <c r="BG73" t="n">
-        <v>15.5</v>
+        <v>19.5</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -14731,7 +14731,7 @@
         <v>3.1</v>
       </c>
       <c r="H74" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="I74" t="n">
         <v>2.54</v>
@@ -14749,7 +14749,7 @@
         <v>1.05</v>
       </c>
       <c r="N74" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O74" t="n">
         <v>1.23</v>
@@ -14758,19 +14758,19 @@
         <v>2.4</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R74" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S74" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T74" t="n">
         <v>1.59</v>
       </c>
       <c r="U74" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="V74" t="n">
         <v>1.65</v>
@@ -14785,7 +14785,7 @@
         <v>14</v>
       </c>
       <c r="Z74" t="n">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AA74" t="n">
         <v>34</v>
@@ -14800,7 +14800,7 @@
         <v>12</v>
       </c>
       <c r="AE74" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AF74" t="n">
         <v>23</v>
@@ -14848,10 +14848,10 @@
         <v>14.5</v>
       </c>
       <c r="AU74" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV74" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW74" t="n">
         <v>21</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -15116,13 +15116,13 @@
         <v>3.3</v>
       </c>
       <c r="G76" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="H76" t="n">
         <v>2.3</v>
       </c>
       <c r="I76" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J76" t="n">
         <v>3.3</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -15346,7 +15346,7 @@
         <v>1.31</v>
       </c>
       <c r="S77" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="T77" t="n">
         <v>1.87</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -15719,7 +15719,7 @@
         <v>1.01</v>
       </c>
       <c r="N79" t="n">
-        <v>1.18</v>
+        <v>1.03</v>
       </c>
       <c r="O79" t="n">
         <v>1.3</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -15931,7 +15931,7 @@
         <v>2.6</v>
       </c>
       <c r="T80" t="n">
-        <v>1.01</v>
+        <v>1.59</v>
       </c>
       <c r="U80" t="n">
         <v>1.01</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -16283,7 +16283,7 @@
         <v>5.5</v>
       </c>
       <c r="H82" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="I82" t="n">
         <v>2.26</v>
@@ -16292,7 +16292,7 @@
         <v>3.2</v>
       </c>
       <c r="K82" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="L82" t="n">
         <v>1.01</v>
@@ -16301,16 +16301,16 @@
         <v>1.01</v>
       </c>
       <c r="N82" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="O82" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P82" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R82" t="n">
         <v>1.33</v>
@@ -16440,7 +16440,7 @@
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -16865,16 +16865,16 @@
         <v>4.1</v>
       </c>
       <c r="H85" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="I85" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J85" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="K85" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="L85" t="n">
         <v>1.55</v>
@@ -16883,13 +16883,13 @@
         <v>1.12</v>
       </c>
       <c r="N85" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O85" t="n">
         <v>1.51</v>
       </c>
       <c r="P85" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Q85" t="n">
         <v>2.52</v>
@@ -16901,13 +16901,13 @@
         <v>4.2</v>
       </c>
       <c r="T85" t="n">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="U85" t="n">
         <v>1.01</v>
       </c>
       <c r="V85" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="W85" t="n">
         <v>1.32</v>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -17059,7 +17059,7 @@
         <v>4.9</v>
       </c>
       <c r="H86" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="I86" t="n">
         <v>1.98</v>
@@ -17077,13 +17077,13 @@
         <v>1.1</v>
       </c>
       <c r="N86" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O86" t="n">
         <v>1.44</v>
       </c>
       <c r="P86" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="Q86" t="n">
         <v>2.36</v>
@@ -17092,7 +17092,7 @@
         <v>1.26</v>
       </c>
       <c r="S86" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="T86" t="n">
         <v>2.08</v>
@@ -17104,7 +17104,7 @@
         <v>2.02</v>
       </c>
       <c r="W86" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="X86" t="n">
         <v>10.5</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -17280,7 +17280,7 @@
         <v>1.78</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R87" t="n">
         <v>1.27</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -17456,7 +17456,7 @@
         <v>3.4</v>
       </c>
       <c r="K88" t="n">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="L88" t="n">
         <v>1.3</v>
@@ -17604,7 +17604,7 @@
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -17662,13 +17662,13 @@
         <v>1.25</v>
       </c>
       <c r="O89" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P89" t="n">
         <v>1.24</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="R89" t="n">
         <v>1.18</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -17832,7 +17832,7 @@
         <v>2.26</v>
       </c>
       <c r="G90" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H90" t="n">
         <v>3.75</v>
@@ -17853,13 +17853,13 @@
         <v>1.1</v>
       </c>
       <c r="N90" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="O90" t="n">
         <v>1.44</v>
       </c>
       <c r="P90" t="n">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="Q90" t="n">
         <v>2.3</v>
@@ -17871,19 +17871,19 @@
         <v>4.3</v>
       </c>
       <c r="T90" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="U90" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="V90" t="n">
         <v>1.34</v>
       </c>
       <c r="W90" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X90" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Y90" t="n">
         <v>12</v>
@@ -17898,7 +17898,7 @@
         <v>8.4</v>
       </c>
       <c r="AC90" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AD90" t="n">
         <v>16</v>
@@ -17910,7 +17910,7 @@
         <v>14</v>
       </c>
       <c r="AG90" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AH90" t="n">
         <v>21</v>
@@ -17922,7 +17922,7 @@
         <v>32</v>
       </c>
       <c r="AK90" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AL90" t="n">
         <v>50</v>
@@ -17931,10 +17931,10 @@
         <v>140</v>
       </c>
       <c r="AN90" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO90" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AP90" t="n">
         <v>9.6</v>
@@ -17946,19 +17946,19 @@
         <v>22</v>
       </c>
       <c r="AS90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AT90" t="n">
         <v>7.4</v>
       </c>
       <c r="AU90" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV90" t="n">
         <v>14.5</v>
       </c>
       <c r="AW90" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX90" t="n">
         <v>11.5</v>
@@ -17970,29 +17970,29 @@
         <v>18</v>
       </c>
       <c r="BA90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BB90" t="n">
         <v>27</v>
       </c>
       <c r="BC90" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BD90" t="n">
         <v>42</v>
       </c>
       <c r="BE90" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BF90" t="n">
         <v>22</v>
       </c>
       <c r="BG90" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -18047,13 +18047,13 @@
         <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="O91" t="n">
         <v>1.34</v>
       </c>
       <c r="P91" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="Q91" t="n">
         <v>1.92</v>
@@ -18074,7 +18074,7 @@
         <v>1.38</v>
       </c>
       <c r="W91" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X91" t="n">
         <v>1000</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -18226,10 +18226,10 @@
         <v>2.5</v>
       </c>
       <c r="I92" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J92" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="K92" t="n">
         <v>3.8</v>
@@ -18265,7 +18265,7 @@
         <v>1.01</v>
       </c>
       <c r="V92" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W92" t="n">
         <v>1.25</v>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -18414,13 +18414,13 @@
         <v>2.14</v>
       </c>
       <c r="G93" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="H93" t="n">
         <v>3.75</v>
       </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J93" t="n">
         <v>3.15</v>
@@ -18435,7 +18435,7 @@
         <v>1.05</v>
       </c>
       <c r="N93" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="O93" t="n">
         <v>1.29</v>
@@ -18444,49 +18444,49 @@
         <v>1.25</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.87</v>
+        <v>1.29</v>
       </c>
       <c r="R93" t="n">
         <v>1.18</v>
       </c>
       <c r="S93" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T93" t="n">
-        <v>1.71</v>
+        <v>1.56</v>
       </c>
       <c r="U93" t="n">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="V93" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="W93" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X93" t="n">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="Y93" t="n">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="Z93" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="AA93" t="n">
         <v>80</v>
       </c>
       <c r="AB93" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC93" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD93" t="n">
         <v>17.5</v>
       </c>
       <c r="AE93" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="AF93" t="n">
         <v>15</v>
@@ -18501,80 +18501,80 @@
         <v>60</v>
       </c>
       <c r="AJ93" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AK93" t="n">
         <v>24</v>
       </c>
       <c r="AL93" t="n">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AM93" t="n">
         <v>100</v>
       </c>
       <c r="AN93" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AO93" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP93" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AQ93" t="n">
         <v>13</v>
       </c>
       <c r="AR93" t="n">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AS93" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT93" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AU93" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV93" t="n">
         <v>14</v>
       </c>
       <c r="AW93" t="n">
-        <v>6.8</v>
+        <v>6.2</v>
       </c>
       <c r="AX93" t="n">
         <v>12</v>
       </c>
       <c r="AY93" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ93" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="BA93" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BB93" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BC93" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="BD93" t="n">
         <v>6</v>
       </c>
-      <c r="BC93" t="n">
-        <v>18</v>
-      </c>
-      <c r="BD93" t="n">
-        <v>6.4</v>
-      </c>
       <c r="BE93" t="n">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="BF93" t="n">
         <v>11.5</v>
       </c>
       <c r="BG93" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -18611,7 +18611,7 @@
         <v>2.52</v>
       </c>
       <c r="H94" t="n">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="I94" t="n">
         <v>4.6</v>
@@ -18620,7 +18620,7 @@
         <v>2.94</v>
       </c>
       <c r="K94" t="n">
-        <v>5.8</v>
+        <v>3.4</v>
       </c>
       <c r="L94" t="n">
         <v>1.01</v>
@@ -18629,13 +18629,13 @@
         <v>1.01</v>
       </c>
       <c r="N94" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="O94" t="n">
-        <v>1.51</v>
+        <v>1.02</v>
       </c>
       <c r="P94" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="Q94" t="n">
         <v>1.52</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -18962,7 +18962,7 @@
       </c>
       <c r="BH95" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -19002,7 +19002,7 @@
         <v>4.6</v>
       </c>
       <c r="I96" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="J96" t="n">
         <v>3.4</v>
@@ -19156,7 +19156,7 @@
       </c>
       <c r="BH96" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -19196,10 +19196,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="I97" t="n">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J97" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="K97" t="n">
         <v>6.4</v>
@@ -19220,7 +19220,7 @@
         <v>3.25</v>
       </c>
       <c r="Q97" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="R97" t="n">
         <v>1.93</v>
@@ -19238,7 +19238,7 @@
         <v>1.11</v>
       </c>
       <c r="W97" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="X97" t="n">
         <v>40</v>
@@ -19256,7 +19256,7 @@
         <v>15</v>
       </c>
       <c r="AC97" t="n">
-        <v>610</v>
+        <v>120</v>
       </c>
       <c r="AD97" t="n">
         <v>34</v>
@@ -19346,11 +19346,11 @@
         <v>3.55</v>
       </c>
       <c r="BG97" t="n">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="BH97" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -19544,7 +19544,7 @@
       </c>
       <c r="BH98" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -19578,16 +19578,16 @@
         <v>1.54</v>
       </c>
       <c r="G99" t="n">
-        <v>2.14</v>
+        <v>2.1</v>
       </c>
       <c r="H99" t="n">
         <v>5</v>
       </c>
       <c r="I99" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="J99" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="K99" t="n">
         <v>6.6</v>
@@ -19599,13 +19599,13 @@
         <v>1.01</v>
       </c>
       <c r="N99" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="O99" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="P99" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="Q99" t="n">
         <v>2.22</v>
@@ -19626,7 +19626,7 @@
         <v>1.11</v>
       </c>
       <c r="W99" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X99" t="n">
         <v>1000</v>
@@ -19738,7 +19738,7 @@
       </c>
       <c r="BH99" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -19796,19 +19796,19 @@
         <v>1.25</v>
       </c>
       <c r="O100" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="P100" t="n">
         <v>1.24</v>
       </c>
       <c r="Q100" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="R100" t="n">
         <v>1.18</v>
       </c>
       <c r="S100" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="T100" t="n">
         <v>1.01</v>
@@ -19932,7 +19932,7 @@
       </c>
       <c r="BH100" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -19969,10 +19969,10 @@
         <v>1.76</v>
       </c>
       <c r="H101" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="I101" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J101" t="n">
         <v>4</v>
@@ -20107,7 +20107,7 @@
         <v>13.5</v>
       </c>
       <c r="BB101" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="BC101" t="n">
         <v>16</v>
@@ -20126,7 +20126,7 @@
       </c>
       <c r="BH101" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -20163,10 +20163,10 @@
         <v>3.85</v>
       </c>
       <c r="H102" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="I102" t="n">
         <v>2.3</v>
-      </c>
-      <c r="I102" t="n">
-        <v>2.32</v>
       </c>
       <c r="J102" t="n">
         <v>3.25</v>
@@ -20205,7 +20205,7 @@
         <v>2.16</v>
       </c>
       <c r="V102" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W102" t="n">
         <v>1.35</v>
@@ -20226,7 +20226,7 @@
         <v>13.5</v>
       </c>
       <c r="AC102" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD102" t="n">
         <v>11</v>
@@ -20320,7 +20320,7 @@
       </c>
       <c r="BH102" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -20354,7 +20354,7 @@
         <v>2.76</v>
       </c>
       <c r="G103" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="H103" t="n">
         <v>2.92</v>
@@ -20384,7 +20384,7 @@
         <v>1.58</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="R103" t="n">
         <v>1.2</v>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="BH103" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -20548,7 +20548,7 @@
         <v>1.76</v>
       </c>
       <c r="G104" t="n">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="H104" t="n">
         <v>4.2</v>
@@ -20560,7 +20560,7 @@
         <v>2.66</v>
       </c>
       <c r="K104" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L104" t="n">
         <v>1.51</v>
@@ -20572,7 +20572,7 @@
         <v>1.35</v>
       </c>
       <c r="O104" t="n">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="P104" t="n">
         <v>1.35</v>
@@ -20596,7 +20596,7 @@
         <v>1.15</v>
       </c>
       <c r="W104" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X104" t="n">
         <v>1000</v>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="BH104" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -20763,13 +20763,13 @@
         <v>1.02</v>
       </c>
       <c r="N105" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="O105" t="n">
         <v>1.42</v>
       </c>
       <c r="P105" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q105" t="n">
         <v>2.06</v>
@@ -20902,7 +20902,7 @@
       </c>
       <c r="BH105" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -21096,7 +21096,7 @@
       </c>
       <c r="BH106" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -21154,22 +21154,22 @@
         <v>4.8</v>
       </c>
       <c r="O107" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P107" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="Q107" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="R107" t="n">
         <v>1.52</v>
       </c>
       <c r="S107" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="T107" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="U107" t="n">
         <v>1.83</v>
@@ -21290,7 +21290,7 @@
       </c>
       <c r="BH107" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -21321,7 +21321,7 @@
         </is>
       </c>
       <c r="F108" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="G108" t="n">
         <v>1.82</v>
@@ -21330,10 +21330,10 @@
         <v>3.5</v>
       </c>
       <c r="I108" t="n">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="J108" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="K108" t="n">
         <v>1000</v>
@@ -21369,7 +21369,7 @@
         <v>1.01</v>
       </c>
       <c r="V108" t="n">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W108" t="n">
         <v>2.2</v>
@@ -21429,31 +21429,31 @@
         <v>1000</v>
       </c>
       <c r="AP108" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ108" t="n">
         <v>13</v>
       </c>
       <c r="AR108" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AS108" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="AT108" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU108" t="n">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV108" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AW108" t="n">
         <v>50</v>
       </c>
       <c r="AX108" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY108" t="n">
         <v>9</v>
@@ -21465,16 +21465,16 @@
         <v>55</v>
       </c>
       <c r="BB108" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BC108" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BD108" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BE108" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="BF108" t="n">
         <v>1.01</v>
@@ -21484,7 +21484,7 @@
       </c>
       <c r="BH108" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
@@ -21678,7 +21678,7 @@
       </c>
       <c r="BH109" t="inlineStr">
         <is>
-          <t>2026-03-07 01:27:45</t>
+          <t>2026-03-07 03:58:44</t>
         </is>
       </c>
     </row>
